--- a/stories/arbres/ATOM-SAN.SOM.001-09.xlsx
+++ b/stories/arbres/ATOM-SAN.SOM.001-09.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Le soir, la maison est calme. La lampe est douce. Ariane bâille. Maman dit : c'est l'heure. Ariane prend le pyjama. Le pyjama a des lunes. Il est doux. Ariane met le pyjama. Un bras. Puis l'autre. Papa ouvre le lit. La couverture est chaude. Ariane se couche. Elle pose la tête. Papa raconte une petite histoire. Ariane écoute. Elle ferme les yeux. C'est le dodo. Maman dit : le corps a besoin de dormir. Ariane respire. Papa baisse la lampe. Ariane est au lit. Le soir, pyjama, dodo.</t>
+          <t>Le soir, la maison est calme. La lampe est douce. Ariane bâille. C'est l'heure. Ariane prend le pyjama. Le pyjama a des lunes. Il est doux. Ariane met le pyjama. Un bras. Puis l'autre. Papa ouvre le lit. La couverture est chaude. Ariane se couche. Elle pose la tête. Papa raconte une petite histoire. Ariane écoute. Elle ferme les yeux. C'est le dodo. Le corps a besoin de dormir. Ariane respire. Papa baisse la lampe. Ariane est au lit. Le soir, pyjama, dodo.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,15 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Le soir, la maison est calme. La lampe est douce. Ariane bâille.
+maman|C'est l'heure.
+narrateur|Ariane prend le pyjama. Le pyjama a des lunes. Il est doux. Ariane met le pyjama. Un bras. Puis l'autre. Papa ouvre le lit. La couverture est chaude. Ariane se couche. Elle pose la tête. Papa raconte une petite histoire. Ariane écoute. Elle ferme les yeux. C'est le dodo.
+maman|Le corps a besoin de dormir.
+narrateur|Ariane respire. Papa baisse la lampe. Ariane est au lit. Le soir, pyjama, dodo.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1469,6 +1494,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Le soir, Ariane va dormir. Que met-elle ?</t>
         </is>
       </c>
     </row>
@@ -1637,6 +1667,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Ariane a mis le pyjama. Elle s'est couchée. Le soir, c'est le dodo.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1799,6 +1834,11 @@
         <v>12</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Papa pose le livre. Ariane respire.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1961,6 +2001,11 @@
         <v>12</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1979,7 +2024,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1996,6 +2041,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.SOM.001-09.xlsx
+++ b/stories/arbres/ATOM-SAN.SOM.001-09.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1314,6 +1319,7 @@
 narrateur|Ariane respire. Papa baisse la lampe. Ariane est au lit. Le soir, pyjama, dodo.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1501,6 +1507,7 @@
           <t>narrateur|Le soir, Ariane va dormir. Que met-elle ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1672,6 +1679,7 @@
           <t>narrateur|Ariane a mis le pyjama. Elle s'est couchée. Le soir, c'est le dodo.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1839,6 +1847,7 @@
           <t>narrateur|Papa pose le livre. Ariane respire.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2006,6 +2015,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2024,7 +2034,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2048,6 +2058,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2062,7 +2086,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2249,6 +2273,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SAN.SOM.001-09.xlsx
+++ b/stories/arbres/ATOM-SAN.SOM.001-09.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Ariane met le pyjama</t>
+          <t>La lune en papier de Mila</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Une lune en papier est collée au mur. Mila met le pyjama aux lunes. Papa raconte. Mila se couche. Soir, pyjama, dodo.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Le soir, la maison est calme. La lampe est douce. Ariane bâille. C'est l'heure. Ariane prend le pyjama. Le pyjama a des lunes. Il est doux. Ariane met le pyjama. Un bras. Puis l'autre. Papa ouvre le lit. La couverture est chaude. Ariane se couche. Elle pose la tête. Papa raconte une petite histoire. Ariane écoute. Elle ferme les yeux. C'est le dodo. Le corps a besoin de dormir. Ariane respire. Papa baisse la lampe. Ariane est au lit. Le soir, pyjama, dodo.</t>
+          <t>Une lune en papier est collée au mur. Elle est un peu froissée. Une chaussette rose dort par terre. Dehors, un grillon chante tout bas. La lampe est douce. Ça sent le savon, encore un peu. Mila vit ici, avec papa et maman. En ce moment, Mila bâille. C'est l'heure, Mila. L'heure de la lune ? L'heure du pyjama. Le pyjama a des lunes. Mila prend le pyjama. Le pyjama a des lunes. Il est doux. Une lune, deux lunes. Oui. Mets le pyjama. Mila met le pyjama. Un bras. Puis l'autre. Bravo, Mila. Tu as mis le pyjama. J'ouvre le lit. Papa ouvre le lit. La couverture est chaude. Mila se couche. Elle pose la tête. La lune du mur veille. Oui. Elle veille. Une petite histoire ? Oui, papa. Papa raconte une petite histoire. Une lune marche tout lentement. Mila écoute. Elle ferme les yeux. C'est le dodo. Le corps a besoin de dormir. Je baisse la lampe. Pyjama, puis dodo. Oui. Bravo. Tu as fait du bon travail. Mila respire. Mila est au lit. Le soir, pyjama, dodo. Le grillon chante encore.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,11 +1324,51 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Le soir, la maison est calme. La lampe est douce. Ariane bâille.
-maman|C'est l'heure.
-narrateur|Ariane prend le pyjama. Le pyjama a des lunes. Il est doux. Ariane met le pyjama. Un bras. Puis l'autre. Papa ouvre le lit. La couverture est chaude. Ariane se couche. Elle pose la tête. Papa raconte une petite histoire. Ariane écoute. Elle ferme les yeux. C'est le dodo.
+          <t>narrateur|Une lune en papier est collée au mur.
+narrateur|Elle est un peu froissée.
+narrateur|Une chaussette rose dort par terre.
+narrateur|Dehors, un grillon chante tout bas.
+narrateur|La lampe est douce.
+narrateur|Ça sent le savon, encore un peu.
+narrateur|Mila vit ici, avec papa et maman.
+narrateur|En ce moment, Mila bâille.
+maman|C'est l'heure, Mila.
+enfant-f|L'heure de la lune ?
+maman|L'heure du pyjama.
+maman|Le pyjama a des lunes.
+narrateur|Mila prend le pyjama.
+narrateur|Le pyjama a des lunes.
+narrateur|Il est doux.
+enfant-f|Une lune, deux lunes.
+maman|Oui. Mets le pyjama.
+narrateur|Mila met le pyjama.
+narrateur|Un bras.
+narrateur|Puis l'autre.
+maman|Bravo, Mila.
+maman|Tu as mis le pyjama.
+papa|J'ouvre le lit.
+narrateur|Papa ouvre le lit.
+narrateur|La couverture est chaude.
+narrateur|Mila se couche.
+narrateur|Elle pose la tête.
+enfant-f|La lune du mur veille.
+papa|Oui. Elle veille.
+papa|Une petite histoire ?
+enfant-f|Oui, papa.
+narrateur|Papa raconte une petite histoire.
+narrateur|Une lune marche tout lentement.
+narrateur|Mila écoute.
+narrateur|Elle ferme les yeux.
+maman|C'est le dodo.
 maman|Le corps a besoin de dormir.
-narrateur|Ariane respire. Papa baisse la lampe. Ariane est au lit. Le soir, pyjama, dodo.</t>
+papa|Je baisse la lampe.
+enfant-f|Pyjama, puis dodo.
+maman|Oui. Bravo.
+maman|Tu as fait du bon travail.
+narrateur|Mila respire.
+narrateur|Mila est au lit.
+narrateur|Le soir, pyjama, dodo.
+narrateur|Le grillon chante encore.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr"/>
@@ -1344,7 +1396,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Le soir, Ariane va dormir. Que met-elle ?</t>
+          <t>Le soir, Mila va dormir. Que met-elle ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1504,7 +1556,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Le soir, Ariane va dormir. Que met-elle ?</t>
+          <t>narrateur|Le soir, Mila va dormir.
+narrateur|Que met-elle ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1532,7 +1585,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Ariane a mis le pyjama. Elle s'est couchée. Le soir, c'est le dodo.</t>
+          <t>Mila a mis le pyjama. Elle s'est couchée. Tu as mis le pyjama aux lunes ? Oui, maman. Bravo, Mila. Le soir, c'est le dodo. La lune en papier veille.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1676,7 +1729,13 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Ariane a mis le pyjama. Elle s'est couchée. Le soir, c'est le dodo.</t>
+          <t>narrateur|Mila a mis le pyjama.
+narrateur|Elle s'est couchée.
+maman|Tu as mis le pyjama aux lunes ?
+enfant-f|Oui, maman.
+maman|Bravo, Mila.
+papa|Le soir, c'est le dodo.
+narrateur|La lune en papier veille.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1704,7 +1763,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Papa pose le livre. Ariane respire.</t>
+          <t>Je pose le livre. Le grillon chante. Oui. Tout bas. Mila respire. Le pyjama est chaud. Tu es bien couchée ? Oui. La chaussette rose attend par terre.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1844,7 +1903,14 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Papa pose le livre. Ariane respire.</t>
+          <t>papa|Je pose le livre.
+enfant-f|Le grillon chante.
+papa|Oui. Tout bas.
+narrateur|Mila respire.
+narrateur|Le pyjama est chaud.
+maman|Tu es bien couchée ?
+enfant-f|Oui.
+narrateur|La chaussette rose attend par terre.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1872,7 +1938,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai mis le pyjama. Bravo. Tu as fait du bon travail. Les lunes veillent. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2012,7 +2078,11 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai mis le pyjama.
+maman|Bravo.
+papa|Tu as fait du bon travail.
+narrateur|Les lunes veillent.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2034,7 +2104,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2072,6 +2142,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.SOM.001-09.xlsx
+++ b/stories/arbres/ATOM-SAN.SOM.001-09.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Une lune en papier est collée au mur. Elle est un peu froissée. Une chaussette rose dort par terre. Dehors, un grillon chante tout bas. La lampe est douce. Ça sent le savon, encore un peu. Mila vit ici, avec papa et maman. En ce moment, Mila bâille. C'est l'heure, Mila. L'heure de la lune ? L'heure du pyjama. Le pyjama a des lunes. Mila prend le pyjama. Le pyjama a des lunes. Il est doux. Une lune, deux lunes. Oui. Mets le pyjama. Mila met le pyjama. Un bras. Puis l'autre. Bravo, Mila. Tu as mis le pyjama. J'ouvre le lit. Papa ouvre le lit. La couverture est chaude. Mila se couche. Elle pose la tête. La lune du mur veille. Oui. Elle veille. Une petite histoire ? Oui, papa. Papa raconte une petite histoire. Une lune marche tout lentement. Mila écoute. Elle ferme les yeux. C'est le dodo. Le corps a besoin de dormir. Je baisse la lampe. Pyjama, puis dodo. Oui. Bravo. Tu as fait du bon travail. Mila respire. Mila est au lit. Le soir, pyjama, dodo. Le grillon chante encore.</t>
+          <t>Une lune en papier est collée au mur. Elle est un peu froissée. Un coin se soulève, tout mince. Une chaussette rose dort par terre. Elle a perdu sa copine. Dehors, un grillon chante tout bas. La lampe est douce. Elle fait un rond sur le plancher. Ça sent le savon, encore un peu. Un crayon est sous la chaise. Mila vit ici, avec papa et maman. En ce moment, Mila bâille. C'est l'heure, Mila. L'heure de la lune ? L'heure du pyjama. Le pyjama a des lunes. Mila prend le pyjama. Le pyjama a des lunes. Il est doux. Une lune, deux lunes. Oui. Mets le pyjama. Mila met le pyjama. Un bras. Puis l'autre. Les lunes du tissu dansent un peu. Elles sont douces, maman. Oui. Tout douces. Bravo, Mila. Tu as mis le pyjama. J'ouvre le lit. Papa ouvre le lit. La couverture est chaude. Mila se couche. Elle pose la tête. La lune du mur veille. Oui. Elle veille. Une petite histoire ? Oui, papa. Papa raconte une petite histoire. Une lune marche tout lentement. Elle traverse le ciel, tout calme. Elle a un pyjama, papa ? Elle a sa lumière. Mila écoute. Elle ferme les yeux. C'est le dodo. Le corps a besoin de dormir. Je baisse la lampe. Pyjama, puis dodo. Oui. Bravo. Mila respire. Mila est au lit. Le soir, pyjama, dodo. Le grillon chante encore. La lampe fait un tout petit rond.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Le &lt;emphasis level="moderate"&gt;soir&lt;/emphasis&gt;, la maison est calme. La lampe est douce. Ariane bâille. Maman dit : c'est l'heure. Ariane prend le pyjama. Le pyjama a des lunes. Il est doux. Ariane met le pyjama. Un bras. Puis l'autre. Papa ouvre le lit. La couverture est chaude. Ariane se couche. Elle pose la tête. Papa raconte une petite histoire. Ariane écoute. Elle ferme les yeux. C'est le dodo. Maman dit : le corps a besoin de dormir. Ariane respire. Papa baisse la lampe. Ariane est au lit. Le soir, pyjama, dodo.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Une lune en papier est collée au mur. Elle est un peu froissée. Un coin se soulève, tout mince. Une chaussette rose dort par terre. Elle a perdu sa copine. Dehors, un grillon chante tout bas. La lampe est douce. Elle fait un rond sur le plancher. Ça sent le savon, encore un peu. Un crayon est sous la chaise. Mila vit ici, avec papa et maman. En ce moment, Mila bâille. C'est l'heure, Mila. L'heure de la lune ? L'heure du pyjama. Le pyjama a des lunes. Mila prend le pyjama. Le pyjama a des lunes. Il est doux. Une lune, deux lunes. Oui. Mets le pyjama. Mila met le pyjama. Un bras. Puis l'autre. Les lunes du tissu dansent un peu. Elles sont douces, maman. Oui. Tout douces. Bravo, Mila. Tu as mis le pyjama. J'ouvre le lit. Papa ouvre le lit. La couverture est chaude. Mila se couche. Elle pose la tête. La lune du mur veille. Oui. Elle veille. Une petite histoire ? Oui, papa. Papa raconte une petite histoire. Une lune marche tout lentement. Elle traverse le ciel, tout calme. Elle a un pyjama, papa ? Elle a sa lumière. Mila écoute. Elle ferme les yeux. C'est le dodo. Le corps a besoin de dormir. Je baisse la lampe. Pyjama, puis dodo. Oui. Bravo. Mila respire. Mila est au lit. Le soir, pyjama, dodo. Le grillon chante encore. La lampe fait un tout petit rond.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1326,10 +1326,14 @@
         <is>
           <t>narrateur|Une lune en papier est collée au mur.
 narrateur|Elle est un peu froissée.
+narrateur|Un coin se soulève, tout mince.
 narrateur|Une chaussette rose dort par terre.
+narrateur|Elle a perdu sa copine.
 narrateur|Dehors, un grillon chante tout bas.
 narrateur|La lampe est douce.
+narrateur|Elle fait un rond sur le plancher.
 narrateur|Ça sent le savon, encore un peu.
+narrateur|Un crayon est sous la chaise.
 narrateur|Mila vit ici, avec papa et maman.
 narrateur|En ce moment, Mila bâille.
 maman|C'est l'heure, Mila.
@@ -1344,6 +1348,9 @@
 narrateur|Mila met le pyjama.
 narrateur|Un bras.
 narrateur|Puis l'autre.
+narrateur|Les lunes du tissu dansent un peu.
+enfant-f|Elles sont douces, maman.
+maman|Oui. Tout douces.
 maman|Bravo, Mila.
 maman|Tu as mis le pyjama.
 papa|J'ouvre le lit.
@@ -1357,6 +1364,9 @@
 enfant-f|Oui, papa.
 narrateur|Papa raconte une petite histoire.
 narrateur|Une lune marche tout lentement.
+narrateur|Elle traverse le ciel, tout calme.
+enfant-f|Elle a un pyjama, papa ?
+papa|Elle a sa lumière.
 narrateur|Mila écoute.
 narrateur|Elle ferme les yeux.
 maman|C'est le dodo.
@@ -1364,14 +1374,13 @@
 papa|Je baisse la lampe.
 enfant-f|Pyjama, puis dodo.
 maman|Oui. Bravo.
-maman|Tu as fait du bon travail.
 narrateur|Mila respire.
 narrateur|Mila est au lit.
 narrateur|Le soir, pyjama, dodo.
-narrateur|Le grillon chante encore.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+narrateur|Le grillon chante encore.
+narrateur|La lampe fait un tout petit rond.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1401,7 +1410,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Le &lt;emphasis level="moderate"&gt;soir&lt;/emphasis&gt;, Ariane va dormir. Que met-elle ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le soir, Mila va dormir. Que met-elle ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1560,7 +1569,6 @@
 narrateur|Que met-elle ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1585,12 +1593,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Mila a mis le pyjama. Elle s'est couchée. Tu as mis le pyjama aux lunes ? Oui, maman. Bravo, Mila. Le soir, c'est le dodo. La lune en papier veille.</t>
+          <t>Mila a mis le pyjama. Elle s'est couchée. Tu as mis le pyjama aux lunes ? Oui, maman. Bravo, Mila. Le soir, c'est le dodo. La lune en papier veille. Le grillon fait encore cri-cri.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Ariane a mis le pyjama. Elle s'est couchée. Le &lt;emphasis level="moderate"&gt;soir&lt;/emphasis&gt;, c'est le dodo.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Mila a mis le pyjama. Elle s'est couchée. Tu as mis le pyjama aux lunes ? Oui, maman. Bravo, Mila. Le soir, c'est le dodo. La lune en papier veille. Le grillon fait encore cri-cri.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1735,10 +1743,10 @@
 enfant-f|Oui, maman.
 maman|Bravo, Mila.
 papa|Le soir, c'est le dodo.
-narrateur|La lune en papier veille.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+narrateur|La lune en papier veille.
+narrateur|Le grillon fait encore cri-cri.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1763,12 +1771,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Je pose le livre. Le grillon chante. Oui. Tout bas. Mila respire. Le pyjama est chaud. Tu es bien couchée ? Oui. La chaussette rose attend par terre.</t>
+          <t>Je pose le livre. Le grillon chante. Oui. Tout bas. Mila respire. Le pyjama est chaud. Tu es bien couchée ? Oui. La chaussette rose attend par terre. On la mettra demain près de l'autre. D'accord, maman. Le coin de la lune se soulève encore. Le papier fait un tout petit bruit.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Papa po&lt;emphasis level="moderate"&gt;se&lt;/emphasis&gt; le livre. Ariane respire.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Je pose le livre. Le grillon chante. Oui. Tout bas. Mila respire. Le pyjama est chaud. Tu es bien couchée ? Oui. La chaussette rose attend par terre. On la mettra demain près de l'autre. D'accord, maman. Le coin de la lune se soulève encore. Le papier fait un tout petit bruit.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1910,10 +1918,13 @@
 narrateur|Le pyjama est chaud.
 maman|Tu es bien couchée ?
 enfant-f|Oui.
-narrateur|La chaussette rose attend par terre.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+narrateur|La chaussette rose attend par terre.
+maman|On la mettra demain près de l'autre.
+enfant-f|D'accord, maman.
+narrateur|Le coin de la lune se soulève encore.
+narrateur|Le papier fait un tout petit bruit.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1938,12 +1949,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'ai mis le pyjama. Bravo. Tu as fait du bon travail. Les lunes veillent. L'histoire est finie.</t>
+          <t>J'ai mis le pyjama. Bravo. Les lunes veillent.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'ai mis le pyjama. Bravo. Les lunes veillent.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2080,12 +2091,9 @@
         <is>
           <t>enfant-f|J'ai mis le pyjama.
 maman|Bravo.
-papa|Tu as fait du bon travail.
-narrateur|Les lunes veillent.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+narrateur|Les lunes veillent.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2104,7 +2112,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2149,6 +2157,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.SOM.001-09.xlsx
+++ b/stories/arbres/ATOM-SAN.SOM.001-09.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Ariane, maman, papa</t>
+          <t>Mila, maman, papa</t>
         </is>
       </c>
     </row>
